--- a/makeup_artist_forms/006_custom_make_up_set_order_form--makeup_artist_forms.xlsx
+++ b/makeup_artist_forms/006_custom_make_up_set_order_form--makeup_artist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,40 +515,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_submission</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Custom Make Up Set Order Form</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>foundation_color_family</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Foundation Color Family</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>color_family</t>
+          <t>eyeshadow_type</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Color Family</t>
+          <t>Eyeshadow Type</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>foundation_choice</t>
+          <t>lip_balm_flavor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Foundation Choice</t>
+          <t>Lip Balm Flavor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>eyeshadow_type</t>
+          <t>special_requests</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eyeshadow Type</t>
+          <t>Special Requests</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>lip_balm_choice</t>
+          <t>form_submission_time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lip Balm Choice</t>
+          <t>Submission Time</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>eyeshadow_color_choice</t>
+          <t>form_submission_day</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eyeshadow Color Choice</t>
+          <t>Submission Day</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>foundation_tone</t>
+          <t>form_submission_days</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Foundation Tone</t>
+          <t>Submission Days</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>lip_balm_flavor</t>
+          <t>free_samples</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lip Balm Flavor</t>
+          <t>Free Samples</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,42 +727,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>foundation_color_family</t>
+          <t>form_submission_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Foundation Color Family</t>
+          <t>Submission Date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>custom_make_up_product_order</t>
+          <t>form_submission</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Custom Make Up Product Order</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Please select all the products you would like to order.</t>
-        </is>
-      </c>
+          <t>Submission</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -772,320 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>special_requests</t>
+          <t>form_submission_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Special Requests</t>
+          <t>Form Submission 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_submission</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>form_submission</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>form_submission</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>form_submission</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>form_submission</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>form_submission</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>form_submission</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>form_submission</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_submission</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_submission</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>form_submission</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_submission</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_submission</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'eye'}</t>
+          <t>eyeshadow</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'eye'}</t>
+          <t>eyeshadow</t>
         </is>
       </c>
     </row>
@@ -1152,709 +849,556 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'face'}</t>
+          <t>face</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'face'}</t>
+          <t>face</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>color_family_choices</t>
+          <t>foundation_color_family_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>color_family_choices</t>
+          <t>foundation_color_family_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'warm'}</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'warm'}</t>
+          <t>warm</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>color_family_choices</t>
+          <t>foundation_color_family_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'cool'}</t>
+          <t>cool</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'cool'}</t>
+          <t>cool</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foundation_choice_choices</t>
+          <t>eyeshadow_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'liquid'}</t>
+          <t>matte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'liquid'}</t>
+          <t>matte</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foundation_choice_choices</t>
+          <t>eyeshadow_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'cream'}</t>
+          <t>metallic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'cream'}</t>
+          <t>metallic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>foundation_choice_choices</t>
+          <t>eyeshadow_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'gel'}</t>
+          <t>duo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'gel'}</t>
+          <t>duo</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>eyeshadow_type_choices</t>
+          <t>lip_balm_flavor_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'matte'}</t>
+          <t>vanilla</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'matte'}</t>
+          <t>vanilla</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>eyeshadow_type_choices</t>
+          <t>lip_balm_flavor_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'metallic'}</t>
+          <t>strawberry</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'metallic'}</t>
+          <t>strawberry</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>eyeshadow_type_choices</t>
+          <t>lip_balm_flavor_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'duo'}</t>
+          <t>blueberry</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'duo'}</t>
+          <t>blueberry</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>lip_balm_choice_choices</t>
+          <t>form_submission_time_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'matte'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'matte'}</t>
+          <t>morning</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lip_balm_choice_choices</t>
+          <t>form_submission_time_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'glossy'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'glossy'}</t>
+          <t>afternoon</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>eyeshadow_color_choice_choices</t>
+          <t>form_submission_day_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'brown'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'brown'}</t>
+          <t>monday</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>eyeshadow_color_choice_choices</t>
+          <t>form_submission_day_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'blue'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'blue'}</t>
+          <t>saturday</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>eyeshadow_color_choice_choices</t>
+          <t>form_submission_days_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'green'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'green'}</t>
+          <t>monday</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>foundation_tone_choices</t>
+          <t>form_submission_days_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'fair'}</t>
+          <t>tuesday</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>foundation_tone_choices</t>
+          <t>form_submission_days_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'medium'}</t>
+          <t>wednesday</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>foundation_tone_choices</t>
+          <t>form_submission_days_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'tan'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'tan'}</t>
+          <t>thursday</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>lip_balm_flavor_choices</t>
+          <t>form_submission_days_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'vanilla'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'vanilla'}</t>
+          <t>friday</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>lip_balm_flavor_choices</t>
+          <t>form_submission_days_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'strawberry'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'strawberry'}</t>
+          <t>saturday</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>lip_balm_flavor_choices</t>
+          <t>form_submission_days_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'blueberry'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'blueberry'}</t>
+          <t>sunday</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>foundation_color_family_choices</t>
+          <t>free_samples_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>foundation_color_family_choices</t>
+          <t>free_samples_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'warm'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'warm'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>foundation_color_family_choices</t>
+          <t>form_submission_date_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'cool'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'cool'}</t>
+          <t>monday</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>custom_make_up_product_order_choices</t>
+          <t>form_submission_date_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'eyeshadow'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'eyeshadow'}</t>
+          <t>tuesday</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>custom_make_up_product_order_choices</t>
+          <t>form_submission_date_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'lip_balm'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'lip_balm'}</t>
+          <t>wednesday</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>custom_make_up_product_order_choices</t>
+          <t>form_submission_date_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'foundation'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'foundation'}</t>
+          <t>thursday</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>form_submission_choices</t>
+          <t>form_submission_date_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'morning'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'morning'}</t>
+          <t>friday</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>form_submission_choices</t>
+          <t>form_submission_date_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'afternoon'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'afternoon'}</t>
+          <t>saturday</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>form_submission_choices</t>
+          <t>form_submission_date_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'monday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'monday'}</t>
+          <t>sunday</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>form_submission_choices</t>
+          <t>form_submission_date_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'saturday'}</t>
+          <t>next</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'saturday'}</t>
+          <t>next</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>form_submission_choices</t>
+          <t>form_submission_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'monday'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'monday'}</t>
+          <t>submit</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>form_submission_choices</t>
+          <t>form_submission_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'tuesday'}</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'tuesday'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>form_submission_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'value':_'wednesday'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'value': 'wednesday'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>form_submission_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'value':_'thursday'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'value': 'thursday'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>form_submission_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'value':_'friday'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'value': 'friday'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>form_submission_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'value':_'saturday'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'value': 'saturday'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>form_submission_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'value':_'sunday'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'value': 'sunday'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>form_submission_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'value':_true}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'value': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>form_submission_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'value':_false}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'value': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>form_submission_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'value':_true}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'value': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>form_submission_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{'value':_false}</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>{'value': False}</t>
+          <t>cancel</t>
         </is>
       </c>
     </row>
